--- a/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/reference_taxa_clusters.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/reference_taxa_clusters.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>0.8019817499587525</v>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>3.203426503814917e-16</v>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>3.203426503814917e-16</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>3.203426503814917e-16</v>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>3.203426503814917e-16</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>3.203426503814917e-16</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>3.203426503814917e-16</v>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1277,17 +1277,17 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>058C</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D15" t="n">
-        <v>3.301698769884566</v>
+        <v>0.9047272710591775</v>
       </c>
       <c r="E15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1296,10 +1296,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.09368399654834478</v>
       </c>
       <c r="H15" t="n">
-        <v>6.525743800901242</v>
+        <v>6.643280158288579</v>
       </c>
       <c r="I15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1311,13 +1311,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.09368399654834478</v>
       </c>
       <c r="M15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.04760230704818257</v>
       </c>
       <c r="O15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1335,17 +1335,17 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>060B</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9047272710591775</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1354,10 +1354,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.09368399654834478</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H16" t="n">
-        <v>6.643280158288579</v>
+        <v>6.643254941572279</v>
       </c>
       <c r="I16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1369,16 +1369,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09368399654834478</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N16" t="n">
-        <v>0.04760230704818257</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.029747343394052</v>
       </c>
       <c r="P16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1393,29 +1393,29 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>064B</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="D17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="E17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.02267182631393</v>
       </c>
       <c r="F17" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.887992562015887</v>
       </c>
       <c r="H17" t="n">
-        <v>6.643254941572279</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1424,19 +1424,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7526899464592227</v>
       </c>
       <c r="L17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="M17" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.244803668756707</v>
       </c>
       <c r="O17" t="n">
-        <v>1.029747343394052</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="P17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1451,26 +1451,26 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>065C</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1.611075341040287</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D18" t="n">
-        <v>1.611075341040287</v>
+        <v>2.712718047919529</v>
       </c>
       <c r="E18" t="n">
-        <v>5.02267182631393</v>
+        <v>5.506032031499436</v>
       </c>
       <c r="F18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G18" t="n">
-        <v>5.887992562015887</v>
+        <v>2.712718047919529</v>
       </c>
       <c r="H18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1482,19 +1482,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7526899464592227</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L18" t="n">
-        <v>1.611075341040287</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N18" t="n">
-        <v>1.244803668756707</v>
+        <v>5.317915032380739</v>
       </c>
       <c r="O18" t="n">
-        <v>1.611075341040287</v>
+        <v>2.712718047919529</v>
       </c>
       <c r="P18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1509,26 +1509,26 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>066A</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="D19" t="n">
-        <v>2.712718047919529</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="E19" t="n">
-        <v>5.506032031499436</v>
+        <v>3.721932779208732</v>
       </c>
       <c r="F19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G19" t="n">
-        <v>2.712718047919529</v>
+        <v>6.304671300699757</v>
       </c>
       <c r="H19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1543,16 +1543,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="M19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N19" t="n">
-        <v>5.317915032380739</v>
+        <v>2.827323338290201</v>
       </c>
       <c r="O19" t="n">
-        <v>2.712718047919529</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1567,26 +1567,26 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>068B</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>1.150242635580613</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D20" t="n">
-        <v>1.150242635580613</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E20" t="n">
-        <v>3.721932779208732</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G20" t="n">
-        <v>6.304671300699757</v>
+        <v>6.051070184214275</v>
       </c>
       <c r="H20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1601,16 +1601,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L20" t="n">
-        <v>1.150242635580613</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>2.827323338290201</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.157604729806445</v>
       </c>
       <c r="P20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1625,7 +1625,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>071B</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1644,10 +1644,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G21" t="n">
-        <v>6.051070184214275</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.339850002884624</v>
       </c>
       <c r="I21" t="n">
         <v>3.203426503814917e-16</v>
@@ -1668,7 +1668,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O21" t="n">
-        <v>5.157604729806445</v>
+        <v>4.392317422778761</v>
       </c>
       <c r="P21" t="n">
         <v>3.203426503814917e-16</v>
@@ -1683,7 +1683,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>073C</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1705,7 +1705,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="H22" t="n">
-        <v>6.339850002884624</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1726,7 +1726,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O22" t="n">
-        <v>4.392317422778761</v>
+        <v>6.658211482751795</v>
       </c>
       <c r="P22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1741,14 +1741,14 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>077B</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.605196984461211</v>
       </c>
       <c r="D23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1760,7 +1760,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.244061423481349</v>
       </c>
       <c r="H23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1781,10 +1781,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.64825093183208</v>
       </c>
       <c r="O23" t="n">
-        <v>6.658211482751795</v>
+        <v>5.258825506031243</v>
       </c>
       <c r="P23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1799,26 +1799,26 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>078B</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>2.605196984461211</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.200819009388096</v>
       </c>
       <c r="E24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.200819009388096</v>
       </c>
       <c r="G24" t="n">
-        <v>3.244061423481349</v>
+        <v>2.291634172573763</v>
       </c>
       <c r="H24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1839,10 +1839,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N24" t="n">
-        <v>5.64825093183208</v>
+        <v>3.334984247712808</v>
       </c>
       <c r="O24" t="n">
-        <v>5.258825506031243</v>
+        <v>6.416427414239525</v>
       </c>
       <c r="P24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1857,7 +1857,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>094C</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1867,19 +1867,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D25" t="n">
-        <v>1.200819009388096</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F25" t="n">
-        <v>1.200819009388096</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G25" t="n">
-        <v>2.291634172573763</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H25" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.426264754702098</v>
       </c>
       <c r="I25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1897,10 +1897,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>3.334984247712808</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O25" t="n">
-        <v>6.416427414239525</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1915,38 +1915,38 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>097ABC</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>2.676761810284823</v>
       </c>
       <c r="E26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8717455093275589</v>
       </c>
       <c r="F26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.500738592794211</v>
       </c>
       <c r="G26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.481908269132582</v>
       </c>
       <c r="H26" t="n">
-        <v>6.426264754702098</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.411291210388779</v>
       </c>
       <c r="K26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.500738592794211</v>
       </c>
       <c r="L26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1955,10 +1955,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.500738592794211</v>
       </c>
       <c r="O26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.803072654025182</v>
       </c>
       <c r="P26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1973,7 +1973,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>098C</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1983,16 +1983,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D27" t="n">
-        <v>2.676761810284823</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8717455093275589</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F27" t="n">
-        <v>0.500738592794211</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G27" t="n">
-        <v>6.481908269132582</v>
+        <v>5.930737337562887</v>
       </c>
       <c r="H27" t="n">
         <v>3.203426503814917e-16</v>
@@ -2001,10 +2001,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J27" t="n">
-        <v>1.411291210388779</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K27" t="n">
-        <v>0.500738592794211</v>
+        <v>4.392317422778761</v>
       </c>
       <c r="L27" t="n">
         <v>3.203426503814917e-16</v>
@@ -2013,10 +2013,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>0.500738592794211</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O27" t="n">
-        <v>1.803072654025182</v>
+        <v>4.392317422778761</v>
       </c>
       <c r="P27" t="n">
         <v>3.203426503814917e-16</v>
@@ -2031,17 +2031,17 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>109C</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.529467388129453</v>
       </c>
       <c r="D28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.776898533069642</v>
       </c>
       <c r="E28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2050,10 +2050,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G28" t="n">
-        <v>5.930737337562887</v>
+        <v>3.623018726983232</v>
       </c>
       <c r="H28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.255073120131111</v>
       </c>
       <c r="I28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2062,7 +2062,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K28" t="n">
-        <v>4.392317422778761</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2071,10 +2071,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.203555779323592</v>
       </c>
       <c r="O28" t="n">
-        <v>4.392317422778761</v>
+        <v>4.443256343088573</v>
       </c>
       <c r="P28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2089,38 +2089,38 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t xml:space="preserve">111C </t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1.529467388129453</v>
+        <v>0.7907111659377324</v>
       </c>
       <c r="D29" t="n">
-        <v>4.776898533069642</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7907111659377324</v>
       </c>
       <c r="F29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G29" t="n">
-        <v>3.623018726983232</v>
+        <v>4.372118352313833</v>
       </c>
       <c r="H29" t="n">
-        <v>2.255073120131111</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.970746195024886</v>
       </c>
       <c r="J29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7907111659377324</v>
       </c>
       <c r="L29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2129,10 +2129,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>5.203555779323592</v>
+        <v>4.881035788519983</v>
       </c>
       <c r="O29" t="n">
-        <v>4.443256343088573</v>
+        <v>5.576380898876536</v>
       </c>
       <c r="P29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2147,38 +2147,38 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>117ABC</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7907111659377324</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7907111659377324</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G30" t="n">
-        <v>4.372118352313833</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I30" t="n">
-        <v>1.970746195024886</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7907111659377324</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2187,10 +2187,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N30" t="n">
-        <v>4.881035788519983</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O30" t="n">
-        <v>5.576380898876536</v>
+        <v>6.658211482751795</v>
       </c>
       <c r="P30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2205,11 +2205,11 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2224,7 +2224,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.886132035441721</v>
       </c>
       <c r="H31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2233,7 +2233,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.345292087952873</v>
       </c>
       <c r="K31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2245,10 +2245,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.861530062208643</v>
       </c>
       <c r="O31" t="n">
-        <v>6.658211482751795</v>
+        <v>3.48595249488999</v>
       </c>
       <c r="P31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2263,11 +2263,11 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>122B</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2282,13 +2282,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.402534852460246</v>
       </c>
       <c r="H32" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8042755291256324</v>
       </c>
       <c r="J32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2303,10 +2303,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.289812447870645</v>
       </c>
       <c r="O32" t="n">
-        <v>6.658211482751795</v>
+        <v>1.518873310263384</v>
       </c>
       <c r="P32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2321,7 +2321,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2331,7 +2331,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.582027209696609</v>
       </c>
       <c r="E33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2340,16 +2340,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G33" t="n">
-        <v>4.886132035441721</v>
+        <v>0.6868421147403698</v>
       </c>
       <c r="H33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.452617933046574</v>
       </c>
       <c r="I33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J33" t="n">
-        <v>2.345292087952873</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2361,10 +2361,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N33" t="n">
-        <v>5.861530062208643</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="O33" t="n">
-        <v>3.48595249488999</v>
+        <v>0.6868421147403698</v>
       </c>
       <c r="P33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2379,32 +2379,32 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="D34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.441858732844736</v>
       </c>
       <c r="E34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="F34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="G34" t="n">
-        <v>4.402534852460246</v>
+        <v>4.592516646115072</v>
       </c>
       <c r="H34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.3657782510295</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8042755291256324</v>
+        <v>1.186447986673725</v>
       </c>
       <c r="J34" t="n">
         <v>3.203426503814917e-16</v>
@@ -2413,16 +2413,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9685979008608663</v>
       </c>
       <c r="M34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N34" t="n">
-        <v>6.289812447870645</v>
+        <v>3.28864350317529</v>
       </c>
       <c r="O34" t="n">
-        <v>1.518873310263384</v>
+        <v>4.648634242809477</v>
       </c>
       <c r="P34" t="n">
         <v>3.203426503814917e-16</v>
@@ -2431,13 +2431,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5641038958234921</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2447,19 +2447,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D35" t="n">
-        <v>3.582027209696609</v>
+        <v>2.345292087952873</v>
       </c>
       <c r="E35" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.195861790625938</v>
       </c>
       <c r="F35" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6868421147403698</v>
+        <v>3.934112064343543</v>
       </c>
       <c r="H35" t="n">
-        <v>6.452617933046574</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2477,10 +2477,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N35" t="n">
-        <v>1.150242635580613</v>
+        <v>2.345292087952873</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6868421147403698</v>
+        <v>6.137252569345645</v>
       </c>
       <c r="P35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2495,32 +2495,32 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>141B</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.399421886369236</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D36" t="n">
-        <v>4.441858732844736</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E36" t="n">
-        <v>0.399421886369236</v>
+        <v>0.4378774756369554</v>
       </c>
       <c r="F36" t="n">
-        <v>0.399421886369236</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G36" t="n">
-        <v>4.592516646115072</v>
+        <v>1.045323990509491</v>
       </c>
       <c r="H36" t="n">
-        <v>4.3657782510295</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I36" t="n">
-        <v>1.186447986673725</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2529,16 +2529,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L36" t="n">
-        <v>0.9685979008608663</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M36" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N36" t="n">
-        <v>3.28864350317529</v>
+        <v>3.745382295550968</v>
       </c>
       <c r="O36" t="n">
-        <v>4.648634242809477</v>
+        <v>6.445763325802663</v>
       </c>
       <c r="P36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2547,38 +2547,38 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R36" t="n">
-        <v>0.5641038958234921</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>146B</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D37" t="n">
-        <v>2.345292087952873</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E37" t="n">
-        <v>3.195861790625938</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G37" t="n">
-        <v>3.934112064343543</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7447429447579256</v>
       </c>
       <c r="J37" t="n">
         <v>3.203426503814917e-16</v>
@@ -2593,10 +2593,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N37" t="n">
-        <v>2.345292087952873</v>
+        <v>3.075948853233299</v>
       </c>
       <c r="O37" t="n">
-        <v>6.137252569345645</v>
+        <v>6.537480770743348</v>
       </c>
       <c r="P37" t="n">
         <v>3.203426503814917e-16</v>
@@ -2611,26 +2611,26 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>150B</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.82797653267369</v>
       </c>
       <c r="D38" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4378774756369554</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F38" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G38" t="n">
-        <v>1.045323990509491</v>
+        <v>1.350716518311988</v>
       </c>
       <c r="H38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2651,10 +2651,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N38" t="n">
-        <v>3.745382295550968</v>
+        <v>2.285688951456035</v>
       </c>
       <c r="O38" t="n">
-        <v>6.445763325802663</v>
+        <v>6.56679155955111</v>
       </c>
       <c r="P38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2669,35 +2669,35 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>GL1</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="D39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.713829095368272</v>
       </c>
       <c r="E39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="F39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.036423408249874</v>
       </c>
       <c r="H39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7447429447579256</v>
+        <v>3.100264123473429</v>
       </c>
       <c r="J39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.896653486982127</v>
       </c>
       <c r="K39" t="n">
         <v>3.203426503814917e-16</v>
@@ -2709,13 +2709,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N39" t="n">
-        <v>3.075948853233299</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="O39" t="n">
-        <v>6.537480770743348</v>
+        <v>3.334984247712809</v>
       </c>
       <c r="P39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="Q39" t="n">
         <v>3.203426503814917e-16</v>
@@ -2727,32 +2727,32 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.82797653267369</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="D40" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="F40" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G40" t="n">
-        <v>1.350716518311988</v>
+        <v>5.144054104230877</v>
       </c>
       <c r="H40" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="J40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2761,22 +2761,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.85065345479636</v>
       </c>
       <c r="M40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.127523751722153</v>
       </c>
       <c r="N40" t="n">
-        <v>2.285688951456035</v>
+        <v>1.410757771901608</v>
       </c>
       <c r="O40" t="n">
-        <v>6.56679155955111</v>
+        <v>5.889810299081591</v>
       </c>
       <c r="P40" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="R40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2785,35 +2785,35 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>1.330645311988472</v>
+        <v>0.4989892776113035</v>
       </c>
       <c r="D41" t="n">
-        <v>3.713829095368272</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E41" t="n">
-        <v>2.010888316142736</v>
+        <v>0.8690393221168372</v>
       </c>
       <c r="F41" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G41" t="n">
-        <v>5.036423408249874</v>
+        <v>5.38919132179204</v>
       </c>
       <c r="H41" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I41" t="n">
-        <v>3.100264123473429</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J41" t="n">
-        <v>4.896653486982127</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2825,13 +2825,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N41" t="n">
-        <v>2.010888316142736</v>
+        <v>1.163285804079277</v>
       </c>
       <c r="O41" t="n">
-        <v>3.334984247712809</v>
+        <v>5.848286675010258</v>
       </c>
       <c r="P41" t="n">
-        <v>2.010888316142736</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2843,32 +2843,32 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9928402084271342</v>
+        <v>1.888578717331577</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5801932565732844</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G42" t="n">
-        <v>4.07395594291159</v>
+        <v>4.662451872030237</v>
       </c>
       <c r="H42" t="n">
-        <v>2.158772140503586</v>
+        <v>0.7447429447579256</v>
       </c>
       <c r="I42" t="n">
-        <v>3.235090048108769</v>
+        <v>1.597901556428655</v>
       </c>
       <c r="J42" t="n">
         <v>3.203426503814917e-16</v>
@@ -2880,53 +2880,53 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M42" t="n">
-        <v>1.797115737552766</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.888578717331577</v>
       </c>
       <c r="O42" t="n">
-        <v>5.963153611563069</v>
+        <v>6.056161680855508</v>
       </c>
       <c r="P42" t="n">
-        <v>0.5801932565732844</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.894457614762477</v>
+        <v>1.233490130219779</v>
       </c>
       <c r="R42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7447429447579256</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D43" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F43" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G43" t="n">
-        <v>5.144054104230877</v>
+        <v>6.131155431277737</v>
       </c>
       <c r="H43" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J43" t="n">
         <v>3.203426503814917e-16</v>
@@ -2935,22 +2935,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L43" t="n">
-        <v>1.85065345479636</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M43" t="n">
-        <v>1.127523751722153</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N43" t="n">
-        <v>1.410757771901608</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O43" t="n">
-        <v>5.889810299081591</v>
+        <v>4.995895601667264</v>
       </c>
       <c r="P43" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R43" t="n">
         <v>3.203426503814917e-16</v>
@@ -2959,32 +2959,32 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4989892776113035</v>
+        <v>1.304854581528421</v>
       </c>
       <c r="D44" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8690393221168372</v>
+        <v>2.584962500721157</v>
       </c>
       <c r="F44" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G44" t="n">
-        <v>5.38919132179204</v>
+        <v>6.082462160191973</v>
       </c>
       <c r="H44" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6674246609131292</v>
       </c>
       <c r="I44" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3719687773869582</v>
       </c>
       <c r="J44" t="n">
         <v>3.203426503814917e-16</v>
@@ -2999,16 +2999,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N44" t="n">
-        <v>1.163285804079277</v>
+        <v>1.745427172914402</v>
       </c>
       <c r="O44" t="n">
-        <v>5.848286675010258</v>
+        <v>4.527247002864868</v>
       </c>
       <c r="P44" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.304854581528421</v>
       </c>
       <c r="R44" t="n">
         <v>3.203426503814917e-16</v>
@@ -3017,32 +3017,32 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D45" t="n">
-        <v>1.888578717331577</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.508772937544713</v>
       </c>
       <c r="F45" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G45" t="n">
-        <v>4.662451872030237</v>
+        <v>5.871125674841771</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7447429447579256</v>
+        <v>0.3183614798671702</v>
       </c>
       <c r="I45" t="n">
-        <v>1.597901556428655</v>
+        <v>0.7997013495141689</v>
       </c>
       <c r="J45" t="n">
         <v>3.203426503814917e-16</v>
@@ -3054,28 +3054,28 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7997013495141689</v>
       </c>
       <c r="N45" t="n">
-        <v>1.888578717331577</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O45" t="n">
-        <v>6.056161680855508</v>
+        <v>5.172396639944554</v>
       </c>
       <c r="P45" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.233490130219779</v>
+        <v>0.9910668752299923</v>
       </c>
       <c r="R45" t="n">
-        <v>0.7447429447579256</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -3091,19 +3091,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="G46" t="n">
-        <v>6.131155431277737</v>
+        <v>5.853451336647058</v>
       </c>
       <c r="H46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="I46" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.212993723334198</v>
       </c>
       <c r="K46" t="n">
         <v>3.203426503814917e-16</v>
@@ -3115,50 +3115,50 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.740240726199067</v>
       </c>
       <c r="O46" t="n">
-        <v>4.995895601667264</v>
+        <v>5.056268219646745</v>
       </c>
       <c r="P46" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="R46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2954558835261716</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>1.304854581528421</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="D47" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E47" t="n">
-        <v>2.584962500721157</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F47" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G47" t="n">
-        <v>6.082462160191973</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6674246609131292</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3719687773869582</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J47" t="n">
         <v>3.203426503814917e-16</v>
@@ -3173,16 +3173,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N47" t="n">
-        <v>1.745427172914402</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="O47" t="n">
-        <v>4.527247002864868</v>
+        <v>4.53743413063857</v>
       </c>
       <c r="P47" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.304854581528421</v>
+        <v>5.506032031499436</v>
       </c>
       <c r="R47" t="n">
         <v>3.203426503814917e-16</v>
@@ -3191,11 +3191,11 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
         <v>3.203426503814917e-16</v>
@@ -3204,19 +3204,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E48" t="n">
-        <v>2.508772937544713</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F48" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G48" t="n">
-        <v>5.871125674841771</v>
+        <v>4.290677160902923</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3183614798671702</v>
+        <v>5.454739923312576</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7997013495141689</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J48" t="n">
         <v>3.203426503814917e-16</v>
@@ -3228,32 +3228,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7997013495141689</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N48" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.635588573791124</v>
       </c>
       <c r="O48" t="n">
-        <v>5.172396639944554</v>
+        <v>4.739539537830033</v>
       </c>
       <c r="P48" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9910668752299923</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R48" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.280107919192735</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
         <v>3.203426503814917e-16</v>
@@ -3265,19 +3265,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F49" t="n">
-        <v>0.540568381362703</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G49" t="n">
-        <v>5.853451336647058</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H49" t="n">
-        <v>0.540568381362703</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I49" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.08037341646402</v>
       </c>
       <c r="J49" t="n">
-        <v>2.212993723334198</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K49" t="n">
         <v>3.203426503814917e-16</v>
@@ -3289,29 +3289,29 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N49" t="n">
-        <v>2.740240726199067</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O49" t="n">
-        <v>5.056268219646745</v>
+        <v>5.101538026462062</v>
       </c>
       <c r="P49" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.540568381362703</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R49" t="n">
-        <v>0.2954558835261716</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
         <v>3.203426503814917e-16</v>
@@ -3326,13 +3326,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G50" t="n">
-        <v>6.086383652788929</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H50" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.462819553754064</v>
       </c>
       <c r="I50" t="n">
-        <v>2.501061243112211</v>
+        <v>1.445799753049531</v>
       </c>
       <c r="J50" t="n">
         <v>3.203426503814917e-16</v>
@@ -3344,35 +3344,35 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M50" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.445799753049531</v>
       </c>
       <c r="N50" t="n">
-        <v>2.267104070142841</v>
+        <v>2.625834782136685</v>
       </c>
       <c r="O50" t="n">
-        <v>4.52568669140555</v>
+        <v>5.149046271766396</v>
       </c>
       <c r="P50" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.430239905922514</v>
+        <v>2.625834782136685</v>
       </c>
       <c r="R50" t="n">
-        <v>0.8855412754150851</v>
+        <v>3.266140316701616</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>3.598259323334614</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D51" t="n">
         <v>3.203426503814917e-16</v>
@@ -3384,7 +3384,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G51" t="n">
-        <v>3.598259323334614</v>
+        <v>3.797347748702223</v>
       </c>
       <c r="H51" t="n">
         <v>3.203426503814917e-16</v>
@@ -3405,16 +3405,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N51" t="n">
-        <v>3.598259323334614</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O51" t="n">
-        <v>4.53743413063857</v>
+        <v>6.434359193595686</v>
       </c>
       <c r="P51" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.506032031499436</v>
+        <v>1.38565369249775</v>
       </c>
       <c r="R51" t="n">
         <v>3.203426503814917e-16</v>
@@ -3423,17 +3423,17 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S70</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.4821516951373809</v>
       </c>
       <c r="D52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.622632918687211</v>
       </c>
       <c r="E52" t="n">
         <v>3.203426503814917e-16</v>
@@ -3442,19 +3442,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G52" t="n">
-        <v>4.290677160902923</v>
+        <v>5.780526748697312</v>
       </c>
       <c r="H52" t="n">
-        <v>5.454739923312576</v>
+        <v>1.757429696725922</v>
       </c>
       <c r="I52" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.757429696725922</v>
       </c>
       <c r="K52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8428990389152713</v>
       </c>
       <c r="L52" t="n">
         <v>3.203426503814917e-16</v>
@@ -3463,32 +3463,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N52" t="n">
-        <v>3.635588573791124</v>
+        <v>3.775936825679039</v>
       </c>
       <c r="O52" t="n">
-        <v>4.739539537830033</v>
+        <v>4.435289923305293</v>
       </c>
       <c r="P52" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.4821516951373809</v>
       </c>
       <c r="R52" t="n">
-        <v>1.280107919192735</v>
+        <v>1.131244533278253</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S72</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5574817642990493</v>
       </c>
       <c r="D53" t="n">
         <v>3.203426503814917e-16</v>
@@ -3500,16 +3500,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G53" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.623018726983231</v>
       </c>
       <c r="H53" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.487612545182457</v>
       </c>
       <c r="I53" t="n">
-        <v>6.08037341646402</v>
+        <v>0.3055025469742512</v>
       </c>
       <c r="J53" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.272079545436801</v>
       </c>
       <c r="K53" t="n">
         <v>3.203426503814917e-16</v>
@@ -3521,16 +3521,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N53" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.008481476755091</v>
       </c>
       <c r="O53" t="n">
-        <v>5.101538026462062</v>
+        <v>4.789256798126342</v>
       </c>
       <c r="P53" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9585800726200192</v>
       </c>
       <c r="R53" t="n">
         <v>3.203426503814917e-16</v>
@@ -3539,14 +3539,14 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S81</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="D54" t="n">
         <v>3.203426503814917e-16</v>
@@ -3558,13 +3558,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G54" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.872231802852783</v>
       </c>
       <c r="H54" t="n">
-        <v>5.462819553754064</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I54" t="n">
-        <v>1.445799753049531</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J54" t="n">
         <v>3.203426503814917e-16</v>
@@ -3576,311 +3576,21 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M54" t="n">
-        <v>1.445799753049531</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N54" t="n">
-        <v>2.625834782136685</v>
+        <v>3.87148525947732</v>
       </c>
       <c r="O54" t="n">
-        <v>5.149046271766396</v>
+        <v>4.741875508290013</v>
       </c>
       <c r="P54" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.625834782136685</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="R54" t="n">
-        <v>3.266140316701616</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G55" t="n">
-        <v>3.797347748702223</v>
-      </c>
-      <c r="H55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="O55" t="n">
-        <v>6.434359193595686</v>
-      </c>
-      <c r="P55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1.38565369249775</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>3</v>
-      </c>
-      <c r="C56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D56" t="n">
-        <v>3.946466801649578</v>
-      </c>
-      <c r="E56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G56" t="n">
-        <v>4.742376604145422</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1.341269817188368</v>
-      </c>
-      <c r="I56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.6901908350612248</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1.911015109459704</v>
-      </c>
-      <c r="L56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N56" t="n">
-        <v>3.350844299056191</v>
-      </c>
-      <c r="O56" t="n">
-        <v>5.416765153834561</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1.654086861375977</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0.6901908350612248</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.155097583764673</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>2</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.4821516951373809</v>
-      </c>
-      <c r="D57" t="n">
-        <v>2.622632918687211</v>
-      </c>
-      <c r="E57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G57" t="n">
-        <v>5.780526748697312</v>
-      </c>
-      <c r="H57" t="n">
-        <v>1.757429696725922</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1.757429696725922</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.8428990389152713</v>
-      </c>
-      <c r="L57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3.775936825679039</v>
-      </c>
-      <c r="O57" t="n">
-        <v>4.435289923305293</v>
-      </c>
-      <c r="P57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0.4821516951373809</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.131244533278253</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.5574817642990493</v>
-      </c>
-      <c r="D58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G58" t="n">
-        <v>3.623018726983231</v>
-      </c>
-      <c r="H58" t="n">
-        <v>5.487612545182457</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.3055025469742512</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1.272079545436801</v>
-      </c>
-      <c r="K58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N58" t="n">
-        <v>4.008481476755091</v>
-      </c>
-      <c r="O58" t="n">
-        <v>4.789256798126342</v>
-      </c>
-      <c r="P58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0.9585800726200192</v>
-      </c>
-      <c r="R58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>2</v>
-      </c>
-      <c r="C59" t="n">
-        <v>1.330645311988472</v>
-      </c>
-      <c r="D59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G59" t="n">
-        <v>5.872231802852783</v>
-      </c>
-      <c r="H59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N59" t="n">
-        <v>3.87148525947732</v>
-      </c>
-      <c r="O59" t="n">
-        <v>4.741875508290013</v>
-      </c>
-      <c r="P59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1.330645311988472</v>
-      </c>
-      <c r="R59" t="n">
         <v>3.203426503814917e-16</v>
       </c>
     </row>
